--- a/QURAN CONTENT/UPDATED OUTPUT/EN_Quran Surah Content (21-6-26).xlsx
+++ b/QURAN CONTENT/UPDATED OUTPUT/EN_Quran Surah Content (21-6-26).xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,1958 +433,1964 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>surah_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>language_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>contents</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Fatihah [1] - Arabic, Translation &amp; Tafsir | الفاتحة","description":"Read the Surah Al-Fatihah [1] with translation and Tafsir. Listen to the Surah Al-Fatihah (الفاتحة) quranic recitation by multiple Qaris. Learn prayer, praise, worship, and guidance"},"heading":{"title":"","description":""},"lessons":["Begin by praising Allah, the Lord of all worlds.","Ask Allah alone for help and worship Him alone.","Seek the straight path in faith, prayer, and daily life.","Remember Allah’s mercy, justice, and complete authority."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="46" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Baqarah [2] - Arabic, Translation &amp; Tafsir | البقرة","description":"Read the Surah Al-Baqarah [2] with translation and Tafsir. Listen to the Surah Al-Baqarah (البقرة) quranic recitation by multiple Qaris. Learn guidance for faith, worship, law, patience, and building a righteous Muslim community"},"heading":{"title":"","description":""},"lessons":["Allah’s guidance is the true path for those who believe, fear Him, and follow His commands.","Faith must be shown through prayer, charity, patience, honesty, and obedience to Allah.","Muslims should avoid hypocrisy, arrogance, and rejecting clear signs after knowing the truth.","Surah Al-Baqarah teaches the importance of justice, family responsibility, lawful earnings, and community life.","Ayat al-Kursi reminds believers of Allah’s perfect knowledge, power, and authority over all creation."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al Imran [3] - Arabic, Translation &amp; Tafsir | آل عمران","description":"Read the Surah Al Imran [3] with translation and Tafsir. Listen to the Surah Al Imran (آل عمران) quranic recitation by multiple Qaris. Learn faith, steadfastness, unity, and trust in Allah."},"heading":{"title":"","description":""},"lessons":["Hold firmly to the rope of Allah and avoid division among Muslims.","Trust Allah in hardship, especially after trials, loss, and fear.","True faith needs patience, obedience, prayer, and sincere repentance.","Follow the message of the prophets and stay firm on Tawheed.","Do not let worldly success or defeat weaken your belief in Allah."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah An-Nisa [4] - Arabic, Translation &amp; Tafsir | النساء","description":"Read the Surah An-Nisa [4] with translation and Tafsir. Listen to the Surah An-Nisa (النساء) quranic recitation by multiple Qaris. Learn Quranic guidance on justice, family rights, inheritance, and social responsibility"},"heading":{"title":"","description":""},"lessons":["Justice must be upheld in family, society, and personal dealings, even when it is difficult.","Women, orphans, and vulnerable people must be treated with fairness, care, and dignity.","Inheritance and family laws are part of Allah’s guidance and should be followed with honesty.","True faith requires obedience to Allah, His Messenger, and sincere concern for the community.","Believers should avoid hypocrisy and build a life based on trust, responsibility, and righteousness."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Ma'idah [5] - Arabic, Translation &amp; Tafsir | المائدة","description":"Read the Surah Al-Ma'idah [5] with translation and Tafsir. Listen to the Surah Al-Ma'idah (المائدة) quranic recitation by multiple Qaris. Learn the importance of fulfilling covenants, obeying Allah’s commands, and following Islamic guidance in daily life."},"heading":{"title":"","description":""},"lessons":["Fulfill promises and agreements, because keeping covenants is a key sign of faith.","Follow Allah’s guidance about halal and haram with sincerity and obedience.","Stand firmly for justice, even when dealing with people you may dislike.","Protect your faith through prayer, worship, and loyalty to Allah.","Learn from past nations and avoid rejecting clear signs after they are known."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-An'am [6] - Arabic, Translation &amp; Tafsir | الأنعام","description":"Read the Surah Al-An'am [6] with translation and Tafsir. Listen to the Surah Al-An'am (الأنعام) quranic recitation by multiple Qaris. Learn the oneness of Allah, rejection of shirk, divine signs, and Islamic guidance."},"heading":{"title":"","description":""},"lessons":["Believe firmly in the oneness of Allah and avoid all forms of shirk.","Reflect on Allah's signs in the heavens, earth, life, and death.","Follow divine guidance instead of customs that oppose the truth.","Trust the message of the prophets and remain patient when facing rejection.","Understand that lawful and unlawful matters belong to Allah's command."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-A'raf [7] - Arabic, Translation &amp; Tafsir | الأعراف","description":"Read the Surah Al-A'raf [7] with translation and Tafsir. Listen to the Surah Al-A'raf (الأعراف) quranic recitation by multiple Qaris. Learn about faith, accountability, and the consequences of rejecting divine guidance."},"heading":{"title":"","description":""},"lessons":["True success comes from believing in Allah, following His guidance, and preparing for the Hereafter.","The stories of earlier nations teach that rejecting the prophets leads to loss and regret.","Pride and disobedience, as shown in the story of Iblis, can take a person away from Allah’s mercy.","Allah’s signs are clear, but people must choose humility, faith, and sincere repentance.","The Quran is a mercy and guidance for those who listen, reflect, and act upon its message."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Anfal [8] - Arabic, Translation &amp; Tafsir | الأنفال","description":"Read the Surah Al-Anfal [8] with translation and Tafsir. Listen to the Surah Al-Anfal (الأنفال) quranic recitation by multiple Qaris. Learn about obedience to Allah, unity, trust in Allah, and guidance related to battle gains."},"heading":{"title":"","description":""},"lessons":["True believers obey Allah and His Messenger with sincerity and humility.","Muslims should remain united, especially during tests and hardship.","Victory comes from Allah, while believers must act with faith, discipline, and patience.","Wealth and gains should be handled with justice, responsibility, and fear of Allah.","Trust in Allah should be joined with preparation, courage, and good conduct."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah At-Tawbah [9] - Arabic, Translation &amp; Tafsir | التوبة","description":"Read the Surah At-Tawbah [9] with translation and Tafsir. Listen to the Surah At-Tawbah (التوبة) quranic recitation by multiple Qaris. Learn about repentance, sincerity, accountability, and loyalty to Allah and His Messenger."},"heading":{"title":"","description":""},"lessons":["Sincere repentance is always open for those who return to Allah with honesty.","True faith requires loyalty to Allah, His Messenger, and the Muslim community.","Hypocrisy is dangerous because it hides disbelief behind outward religious actions.","Believers should support truth, justice, and the needs of the community.","Allah values sincerity, sacrifice, and obedience more than empty claims."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Yunus [10] - Arabic, Translation &amp; Tafsir | يونس","description":"Read the Surah Yunus [10] with translation and Tafsir. Listen to the Surah Yunus (يونس) quranic recitation by multiple Qaris. Learn Allah’s oneness, revelation, resurrection, and trust in His mercy and guidance."},"heading":{"title":"","description":""},"lessons":["Believe firmly in the oneness of Allah and worship Him alone.","Trust the truth of the Quran and follow its guidance with sincerity.","Remember that worldly life is temporary, while the Hereafter is real.","Turn to Allah in repentance before punishment or regret comes.","Have patience like the prophets and rely on Allah during hardship."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Hud [11] - Arabic, Translation &amp; Tafsir | هود","description":"Read the Surah Hud [11] with translation and Tafsir. Listen to the Surah Hud (هود) quranic recitation by multiple Qaris. Learn lessons of Tawhid, patience, prophetic warnings, and Allah’s justice."},"heading":{"title":"","description":""},"lessons":["Stay firm upon Tawhid and worship Allah alone, even when people reject the truth.","Be patient during hardship, as the prophets remained patient while calling their people to guidance.","Trust Allah’s justice, because every nation is accountable for its belief and actions.","Seek forgiveness and turn back to Allah, as sincere repentance opens the way to mercy.","Do not follow arrogance or denial, because rejecting clear signs leads to loss."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Yusuf [12] - Arabic, Translation &amp; Tafsir | يوسف","description":"Read the Surah Yusuf [12] with translation and Tafsir. Listen to the Surah Yusuf (يوسف) quranic recitation by multiple Qaris. Learn patience, trust in Allah, and divine wisdom through the story of Prophet Yusuf."},"heading":{"title":"","description":""},"lessons":["Trust Allah’s plan, even when life feels painful or unclear.","Patience during hardship brings strength, wisdom, and hope.","Protecting oneself from sin is a sign of true faith and fear of Allah.","Forgiveness is a noble quality, even after deep personal pain.","Jealousy can destroy family ties, so believers should purify their hearts."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Ar-Ra'd [13] - Arabic, Translation &amp; Tafsir | الرعد","description":"Read the Surah Ar-Ra'd [13] with translation and Tafsir. Listen to the Surah Ar-Ra'd (الرعد) quranic recitation by multiple Qaris. Learn Allah's signs in creation, the truth of revelation, and guidance for faith and patience."},"heading":{"title":"","description":""},"lessons":["Allah's signs in the sky, earth, thunder, rain, and nature remind believers of His perfect power and wisdom.","True peace comes through remembering Allah, trusting Him, and staying firm on faith.","The Quran is the truth from Allah, and guidance comes to those who sincerely seek it.","Patience, prayer, charity, and good conduct are qualities of those who earn Allah's pleasure.","Falsehood may appear strong for a time, but truth remains and benefits people."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Ibrahim [14] - Arabic, Translation &amp; Tafsir | إبراهيم","description":"Read the Surah Ibrahim [14] with translation and Tafsir. Listen to the Surah Ibrahim (إبراهيم) quranic recitation by multiple Qaris. Learn faith, gratitude, tawhid, and the consequences of accepting or rejecting Allah’s guidance."},"heading":{"title":"","description":""},"lessons":["True guidance comes from Allah, and the Quran leads people from darkness to light.","Gratitude increases Allah’s blessings, while ingratitude leads to loss and hardship.","The stories of the prophets teach patience, courage, and trust in Allah during hardship.","Ibrahim’s supplication shows the importance of prayer, family guidance, and love for worship.","The Surah reminds believers that the Hereafter is real and every person will answer for their choices."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Hijr [15] - Arabic, Translation &amp; Tafsir | الحجر","description":"Read the Surah Al-Hijr [15] with translation and Tafsir. Listen to the Surah Al-Hijr (الحجر) quranic recitation by multiple Qaris. Learn Allah’s protection of the Quran, warnings from past nations, patience, mercy, and certainty in faith."},"heading":{"title":"","description":""},"lessons":["Allah has promised to protect and preserve the Holy Quran from corruption.","Pride and arrogance, as shown by Iblis, lead a person away from Allah’s mercy.","The stories of past nations remind believers to avoid denial and rebellion.","Allah’s mercy is vast, but His punishment is real for those who reject the truth.","Believers should worship Allah with patience and certainty until death comes."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah An-Nahl [16] - Arabic, Translation &amp; Tafsir | النحل","description":"Read the Surah An-Nahl [16] with translation and Tafsir. Listen to the Surah An-Nahl (النحل) quranic recitation by multiple Qaris. Learn the main theme of Allah's blessings, tawhid, gratitude, revelation, and Islamic guidance."},"heading":{"title":"","description":""},"lessons":["Recognize Allah’s countless blessings and respond with sincere gratitude.","Believe in the oneness of Allah and avoid all forms of shirk.","Follow the Quran as divine guidance for faith, worship, and daily conduct.","Use Allah’s provisions in a halal way and avoid false claims about what is lawful or unlawful.","Be patient, wise, and gentle when inviting others to the path of Allah."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Isra [17] - Arabic, Translation &amp; Tafsir | الإسراء","description":"Read the Surah Al-Isra [17] with translation and Tafsir. Listen to the Surah Al-Isra (الإسراء) quranic recitation by multiple Qaris. Learn Allah’s guidance on faith, worship, moral responsibility, and the journey of Isra."},"heading":{"title":"","description":""},"lessons":["Allah alone deserves worship, and every believer must avoid shirk and follow pure Tawheed.","Respecting parents, speaking kindly, and caring for family are major Islamic duties.","Muslims should avoid arrogance, injustice, wastefulness, and harmful actions in daily life.","The Quran is a source of healing, mercy, guidance, and truth for sincere believers.","Every person is responsible for their actions and will be judged fairly by Allah."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Kahf [18] - Arabic, Translation &amp; Tafsir | الكهف","description":"Read the Surah Al-Kahf [18] with translation and Tafsir. Listen to the Surah Al-Kahf (الكهف) quranic recitation by multiple Qaris. Learn the trials of faith, wealth, knowledge, and power, and the need for Allah’s guidance."},"heading":{"title":"","description":""},"lessons":["True faith needs patience, especially when a believer faces pressure or hardship.","Wealth and worldly success are tests, so they should never make a person forget Allah.","Human knowledge is limited, and believers should stay humble before Allah’s wisdom.","Power is a trust from Allah and must be used with justice and mercy.","The Hereafter is real, and this life should be lived with faith, good deeds, and accountability."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Maryam [19] - Arabic, Translation &amp; Tafsir | مريم","description":"Read the Surah Maryam [19] with translation and Tafsir. Listen to the Surah Maryam (مريم) quranic recitation by multiple Qaris. Learn Allah’s mercy, His power to create, the story of Maryam and Prophet Isa, and guidance on faith and the Hereafter."},"heading":{"title":"","description":""},"lessons":["Allah’s mercy reaches His sincere servants, even when their hopes seem impossible.","The birth of Prophet Isa shows Allah’s complete power to create as He wills.","Maryam’s modesty, patience, and trust in Allah are examples of strong faith.","Prophets called people to worship Allah alone and avoid shirk.","The Surah reminds us to prepare for the Hereafter through faith, prayer, and righteous deeds."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Taha [20] - Arabic, Translation &amp; Tafsir | طه","description":"Read the Surah Taha [20] with translation and Tafsir. Listen to the Surah Taha (طه) quranic recitation by multiple Qaris. Learn Allah’s guidance, the story of Prophet Musa, prayer, patience, and accountability."},"heading":{"title":"","description":""},"lessons":["The Quran was revealed as guidance and mercy, not as a source of hardship.","Prophet Musa’s story teaches trust in Allah, courage, and patience during trials.","Regular prayer helps believers remember Allah and stay firm on the right path.","Pride and rejection of truth, like the attitude of Pharaoh, lead to loss.","Worldly life is temporary, while true success is in obeying Allah and preparing for the Hereafter."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Anbiya [21] - Arabic, Translation &amp; Tafsir | الأنبياء","description":"Read the Surah Al-Anbiya [21] with translation and Tafsir. Listen to the Surah Al-Anbiya (الأنبياء) quranic recitation by multiple Qaris. Learn about Allah’s oneness, prophethood, resurrection, and guidance from the lives of the Prophets."},"heading":{"title":"","description":""},"lessons":["Allah alone is worthy of worship, and all prophets called people to the same truth of Tawheed.","The Day of Judgment is real, so every person should live with faith, responsibility, and awareness of accountability.","The stories of the prophets teach patience, trust in Allah, and firmness during hardship.","Allah’s mercy is shown through revelation, guidance, and the sending of prophets to guide humanity.","False gods and worldly pride cannot save anyone; true success comes through sincere faith and righteous actions."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Hajj [22] - Arabic, Translation &amp; Tafsir | الحج","description":"Read the Surah Al-Hajj [22] with translation and Tafsir. Listen to the Surah Al-Hajj (الحج) quranic recitation by multiple Qaris. Learn the call to worship Allah, prepare for the Day of Judgment, honor Hajj, and live with true faith and obedience."},"heading":{"title":"","description":""},"lessons":["Surah Al-Hajj reminds believers to fear Allah and prepare for the Day of Judgment.","The Surah teaches that Hajj is a sign of obedience, unity, humility, and sincere worship.","It explains that sacrifice is not about meat or blood, but about taqwa and devotion to Allah.","Surah Al-Hajj calls people to defend truth, establish prayer, give zakat, and hold firmly to Allah.","It shows that Allah gives victory and help to those who believe, worship Him, and stay patient."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Mu'minun [23] - Arabic, Translation &amp; Tafsir | المؤمنون","description":"Read the Surah Al-Mu'minun [23] with translation and Tafsir. Listen to the Surah Al-Mu'minun (المؤمنون) quranic recitation by multiple Qaris. Learn the qualities of true believers, Allah’s signs, resurrection, and accountability."},"heading":{"title":"","description":""},"lessons":["True success begins with faith, humility in prayer, avoiding vain talk, giving zakah, guarding chastity, and keeping trusts.","Surah Al-Mu'minun reminds us that Allah created human life with wisdom, and every person will return to Him.","The stories of earlier prophets teach patience, trust in Allah, and firmness when people reject the truth.","Worldly life is temporary, while the Hereafter is real and deserves serious preparation.","Believers should seek protection from arrogance, heedlessness, and following desires that lead away from guidance."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah An-Nur [24] - Arabic, Translation &amp; Tafsir | النور","description":"Read the Surah An-Nur [24] with translation and Tafsir. Listen to the Surah An-Nur (النور) quranic recitation by multiple Qaris. Learn Allah’s light, modesty, family ethics, and social guidance."},"heading":{"title":"","description":""},"lessons":["Allah guides believers through His light, and true guidance comes from faith, obedience, and sincerity.","Muslims must protect modesty, purity, and respectful behavior in personal and social life.","False accusations, gossip, and spreading shame are serious sins that harm families and society.","Islam teaches privacy, good manners, and permission before entering homes.","A strong Muslim community is built on truth, justice, repentance, and respect for Allah’s commands."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Furqan [25] - Arabic, Translation &amp; Tafsir | الفرقان","description":"Read the Surah Al-Furqan [25] with translation and Tafsir. Listen to the Surah Al-Furqan (الفرقان) quranic recitation by multiple Qaris. Learn how the Quran separates truth from falsehood and guides believers to righteous living."},"heading":{"title":"","description":""},"lessons":["The Quran is the true criterion that helps believers separate right from wrong.","Rejecting Allah’s signs leads to spiritual loss, while sincere faith brings guidance.","The servants of the Most Merciful live with humility, patience, prayer, and moral discipline.","True believers avoid arrogance, false speech, wastefulness, and sinful behavior.","Dua, repentance, and trust in Allah are key parts of a guided Muslim life."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="27" ht="46" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Ash-Shu'ara [26] - Arabic, Translation &amp; Tafsir | الشعراء","description":"Read the Surah Ash-Shu'ara [26] with translation and Tafsir. Listen to the Surah Ash-Shu'ara (الشعراء) quranic recitation by multiple Qaris. Learn the truth of divine revelation, the stories of the Prophets, and the warning against rejecting Allah's guidance."},"heading":{"title":"","description":""},"lessons":["Allah sent His messengers with clear guidance, and rejecting them leads to loss.","The stories of the Prophets teach patience, trust in Allah, and courage in calling to truth.","Faith is not based on poetry, magic, or false speech, but on the clear revelation of the Holy Quran.","Power, wealth, and status cannot save a nation that denies Allah's signs.","True believers follow guidance, speak truth, and avoid misleading words and actions."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="28" ht="46" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah An-Naml [27] - Arabic, Translation &amp; Tafsir | النمل","description":"Read the Surah An-Naml [27] with translation and Tafsir. Listen to the Surah An-Naml (النمل) quranic recitation by multiple Qaris. Learn about Allah's signs, Tawhid, prophethood, gratitude, and accountability."},"heading":{"title":"","description":""},"lessons":["True faith begins with recognizing Allah’s signs in creation and revelation.","Power and knowledge are blessings from Allah, so believers should respond with gratitude and humility.","The story of Prophet Sulayman teaches wise leadership, justice, and respect for Allah’s creatures.","The Queen of Sheba’s response shows that sincere people accept truth when clear guidance reaches them.","Rejecting Allah’s messengers leads to loss, while faith and obedience bring guidance and success."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="29" ht="46" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Qasas [28] - Arabic, Translation &amp; Tafsir | القصص","description":"Read the Surah Al-Qasas [28] with translation and Tafsir. Listen to the Surah Al-Qasas (القصص) quranic recitation by multiple Qaris. Learn the story of Prophet Musa, Allah’s support for the oppressed, and guidance against pride and worldly attachment."},"heading":{"title":"","description":""},"lessons":["Allah protects and supports the believers, even when they seem weak against powerful oppressors.","The story of Prophet Musa teaches patience, courage, trust in Allah, and the value of righteous action.","Worldly wealth, like the wealth of Qarun, becomes harmful when it leads to pride and forgetfulness of Allah.","True success is not based on power, status, or money, but on faith, obedience, and the Hereafter.","Allah’s plan is always wise, even when people cannot see the outcome at the beginning."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="30" ht="46" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Ankabut [29] - Arabic, Translation &amp; Tafsir | العنكبوت","description":"Read the Surah Al-Ankabut [29] with translation and Tafsir. Listen to the Surah Al-Ankabut (العنكبوت) quranic recitation by multiple Qaris. Learn how trials test faith and how Allah guides those who strive for Him."},"heading":{"title":"","description":""},"lessons":["Faith is not only a claim; believers may be tested to show sincerity and patience.","Relying on false gods or weak supports is like trusting the fragile house of a spider.","Prayer protects the heart and helps a believer stay away from shameful and wrong actions.","Allah supports those who strive in His path and seek guidance with sincerity.","The stories of past prophets remind us to stay firm even when truth is rejected."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="31" ht="46" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Ar-Rum [30] - Arabic, Translation &amp; Tafsir | الروم","description":"Read the Surah Ar-Rum [30] with translation and Tafsir. Listen to the Surah Ar-Rum (الروم) quranic recitation by multiple Qaris. Learn Allah’s signs in creation, history, resurrection, and His promise of truth."},"heading":{"title":"","description":""},"lessons":["Allah controls the rise and fall of nations, and His promise always comes true.","The signs of Allah are found in creation, human life, languages, sleep, rain, and the heavens and earth.","Faith in resurrection helps a believer live with purpose, patience, and accountability.","Islam agrees with the pure human nature, known as fitrah, which calls people to worship Allah alone.","Hardship and defeat can be followed by victory when believers trust Allah and stay firm."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="32" ht="46" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Luqman [31] - Arabic, Translation &amp; Tafsir | لقمان","description":"Read the Surah Luqman [31] with translation and Tafsir. Listen to the Surah Luqman (لقمان) quranic recitation by multiple Qaris. Learn the wise guidance of Luqman, Tawhid, gratitude, prayer, humility, and accountability."},"heading":{"title":"","description":""},"lessons":["True wisdom begins with believing in Allah alone and avoiding shirk.","Gratitude to Allah and kindness to parents are key parts of Islamic character.","Prayer, patience, and advising others with goodness are signs of strong faith.","A believer should avoid pride and speak with humility and balance.","Allah knows every hidden deed, so Muslims should live with accountability."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="33" ht="46" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah As-Sajdah [32] - Arabic, Translation &amp; Tafsir | السجدة","description":"Read the Surah As-Sajdah [32] with translation and Tafsir. Listen to the Surah As-Sajdah (السجدة) quranic recitation by multiple Qaris. Learn Allah’s signs, revelation, resurrection, and humble prostration."},"heading":{"title":"","description":""},"lessons":["True believers respond to Allah’s signs with humility, prostration, praise, and obedience.","The Surah reminds us that the Holy Quran is a true revelation from Allah, not a human-made message.","Life, death, and resurrection are all under Allah’s control, so every person should prepare for the Hereafter.","Sincere worship includes leaving pride, praying with humility, and trusting Allah’s promise.","The final outcome of believers and rejecters is not the same, so faith must lead to righteous action."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="34" ht="46" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Ahzab [33] - Arabic, Translation &amp; Tafsir | الأحزاب","description":"Read the Surah Al-Ahzab [33] with translation and Tafsir. Listen to the Surah Al-Ahzab (الأحزاب) quranic recitation by multiple Qaris. Learn its guidance on faith, obedience to Allah, the Prophet’s example, family rules, and trust during trials."},"heading":{"title":"","description":""},"lessons":["Trust Allah during fear, pressure, and hardship, as shown during the Battle of the Confederates.","Follow the Prophet Muhammad صلى الله عليه وسلم as the best example in faith, patience, worship, and character.","Obey Allah and His Messenger in personal, family, and social matters.","Protect modesty, honor, and respectful conduct in Muslim family and community life.","Speak truthfully and responsibly, because sincere speech leads to righteous actions."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="35" ht="46" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Saba [34] - Arabic, Translation &amp; Tafsir | سبأ","description":"Read the Surah Saba [34] with translation and Tafsir. Listen to the Surah Saba (سبأ) quranic recitation by multiple Qaris. Learn Allah’s complete knowledge, gratitude, resurrection, and accountability."},"heading":{"title":"","description":""},"lessons":["True blessings should lead a believer to gratitude, not pride or forgetfulness.","Allah knows everything in the heavens and the earth, including what people hide and reveal.","Worldly power and wealth cannot save anyone without faith and righteous deeds.","The stories of Prophet Dawud, Prophet Sulayman, and the people of Saba teach obedience, gratitude, and accountability.","Resurrection and judgment are certain, and every person will answer for their choices."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="36" ht="46" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Fatir [35] - Arabic, Translation &amp; Tafsir | فاطر","description":"Read the Surah Fatir [35] with translation and Tafsir. Listen to the Surah Fatir (فاطر) quranic recitation by multiple Qaris. Learn Allah’s power as the Originator of creation, Tawhid, resurrection, and accountability."},"heading":{"title":"","description":""},"lessons":["Allah alone is the Originator of the heavens and the earth, so worship and trust should be directed only to Him.","The signs in creation remind believers of Allah’s wisdom, mercy, and complete control over all things.","Worldly life can deceive people, but the Hereafter is real and every soul will be judged for its deeds.","True honor comes from faith, righteous actions, and sincere remembrance of Allah.","Knowledge should lead to humility and fear of Allah, not pride or neglect."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="37" ht="46" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Yasin [36] - Arabic, Translation &amp; Tafsir | يس","description":"Read the Surah Yasin [36] with translation and Tafsir. Listen to the Surah Yasin (يس) quranic recitation by multiple Qaris. Learn about Allah's oneness, resurrection, prophethood, and accountability."},"heading":{"title":"","description":""},"lessons":["Believe in the oneness of Allah and recognize His signs in creation.","Follow the message of the prophets with sincerity and humility.","Remember that every person will be raised again and held accountable.","Reflect on the Quran as a source of warning, mercy, and guidance.","Do good deeds with faith, knowing that Allah records every action."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="38" ht="46" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah As-Saffat [37] - Arabic, Translation &amp; Tafsir | الصافات","description":"Read the Surah As-Saffat [37] with translation and Tafsir. Listen to the Surah As-Saffat (الصافات) quranic recitation by multiple Qaris. Learn the oneness of Allah, resurrection, ranks of angels, and lessons from the prophets."},"heading":{"title":"","description":""},"lessons":["Believe firmly in the oneness of Allah and avoid all forms of shirk.","Remember that resurrection, judgment, Paradise, and Hell are real.","Learn patience and trust in Allah from the stories of the prophets.","Obey Allah sincerely, as shown in the example of Prophet Ibrahim and his son.","Know that truth will prevail, even when believers face rejection."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="39" ht="46" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Sad [38] - Arabic, Translation &amp; Tafsir | ص","description":"Read the Surah Sad [38] with translation and Tafsir. Listen to the Surah Sad (ص) quranic recitation by multiple Qaris. Learn the message of Tawhid, sincere repentance, patience, and the warning against pride."},"heading":{"title":"","description":""},"lessons":["Pride can stop a person from accepting the truth, so believers should stay humble before Allah.","The stories of Prophet Dawud, Sulayman, and Ayyub teach repentance, gratitude, patience, and trust in Allah.","Allah honors sincere servants who turn back to Him after mistakes.","The story of Adam and Iblis shows that arrogance and disobedience lead to loss.","The Quran is a reminder for those who want guidance and a clear path in life."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="40" ht="46" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Az-Zumar [39] - Arabic, Translation &amp; Tafsir | الزمر","description":"Read the Surah Az-Zumar [39] with translation and Tafsir. Listen to the Surah Az-Zumar (الزمر) quranic recitation by multiple Qaris. Learn the call to sincere worship of Allah, repentance, and the final gathering of people in groups."},"heading":{"title":"","description":""},"lessons":["Worship Allah alone with sincerity and avoid all forms of shirk.","Never lose hope in Allah’s mercy, because sincere repentance is always open.","The Quran guides those who listen carefully and follow the best of its message.","Worldly life is temporary, while the Hereafter is the real and lasting outcome.","On the Day of Judgment, people will be gathered in groups according to their deeds and faith."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="41" ht="46" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Ghafir [40] - Arabic, Translation &amp; Tafsir | غافر","description":"Read the Surah Ghafir [40] with translation and Tafsir. Listen to the Surah Ghafir (غافر) quranic recitation by multiple Qaris. Learn Allah’s forgiveness, the call to repentance, and the truth of the Day of Judgment."},"heading":{"title":"","description":""},"lessons":["Allah is the Forgiver of sins and accepts sincere repentance from His servants.","True faith means trusting Allah, even when truth is opposed by powerful people.","Pride and rejection of Allah’s signs lead people away from guidance.","The story of the believing man from Pharaoh’s family teaches courage in defending truth.","The Day of Judgment is real, and every person will be judged with perfect justice."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="42" ht="46" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Fussilat [41] - Arabic, Translation &amp; Tafsir | فصلت","description":"Read the Surah Fussilat [41] with translation and Tafsir. Listen to the Surah Fussilat (فصلت) quranic recitation by multiple Qaris. Learn how the clear revelation of the Quran explains Allah’s signs, calls to Tawhid, and warns against denial."},"heading":{"title":"","description":""},"lessons":["The Quran is a clear and detailed message from Allah, guiding people toward truth and faith.","Allah’s signs in the heavens, earth, and human life remind us to believe in His power and wisdom.","Rejecting divine guidance leads to loss, while sincere faith and righteous deeds bring hope and mercy.","Calling others to Allah should be done with patience, wisdom, and good character.","True believers remain firm, trust Allah, and seek His forgiveness in daily life."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="43" ht="46" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Ash-Shura [42] - Arabic, Translation &amp; Tafsir | الشورى","description":"Read the Surah Ash-Shura [42] with translation and Tafsir. Listen to the Surah Ash-Shura (الشورى) quranic recitation by multiple Qaris. Learn Allah’s revelation, consultation, accountability, and reliance on Him."},"heading":{"title":"","description":""},"lessons":["Allah alone controls creation, revelation, mercy, and final judgment.","Muslims should make important decisions with consultation, wisdom, and trust in Allah.","True believers avoid major sins, forgive others, and control anger.","Worldly life is temporary, while the reward with Allah is better and lasting.","Revelation is a mercy and guidance that calls people to worship Allah alone."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="44" ht="46" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Az-Zukhruf [43] - Arabic, Translation &amp; Tafsir | الزخرف","description":"Read the Surah Az-Zukhruf [43] with translation and Tafsir. Listen to the Surah Az-Zukhruf (الزخرف) quranic recitation by multiple Qaris. Learn the danger of worldly pride, the truth of Tawheed, and the call to follow Allah’s guidance."},"heading":{"title":"","description":""},"lessons":["Worldly wealth and beauty are temporary and should never replace faith in Allah.","True honor comes from Tawheed, not from status, gold, or social power.","Blindly following ancestors or society can lead people away from the truth.","The stories of earlier messengers show that rejection of guidance has serious results.","Believers should hold firmly to the Quran as clear guidance for daily life."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="45" ht="46" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Ad-Dukhan [44] - Arabic, Translation &amp; Tafsir | الدخان","description":"Read the Surah Ad-Dukhan [44] with translation and Tafsir. Listen to the Surah Ad-Dukhan (الدخان) quranic recitation by multiple Qaris. Learn about Allah’s warning, the truth of the Quran, resurrection, and the final outcome of the righteous and the rejecters."},"heading":{"title":"","description":""},"lessons":["The Quran is a clear revelation from Allah and a source of guidance for those who reflect.","Rejecting Allah’s signs leads to loss, as shown through the warning given to Pharaoh and his people.","The Hereafter is real, and every person will face the result of their faith and actions.","True safety comes through belief, repentance, and obedience to Allah.","The righteous will be honored with peace, mercy, and reward from Allah."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="46" ht="46" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Jathiyah [45] - Arabic, Translation &amp; Tafsir | الجاثية","description":"Read the Surah Al-Jathiyah [45] with translation and Tafsir. Listen to the Surah Al-Jathiyah (الجاثية) quranic recitation by multiple Qaris. Learn the signs of Allah, the truth of revelation, resurrection, and accountability on the Day of Judgment."},"heading":{"title":"","description":""},"lessons":["Allah’s signs in the heavens, earth, and human life invite sincere reflection and faith.","The Quran is true guidance from Allah, and believers should follow it with humility.","Every person will be judged for their deeds, and no one can escape accountability.","Following desires instead of revelation leads people away from truth and guidance.","The Day of Judgment is real, and all nations will kneel before Allah’s final judgment."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="47" ht="46" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Ahqaf [46] - Arabic, Translation &amp; Tafsir | الأحقاف","description":"Read the Surah Al-Ahqaf [46] with translation and Tafsir. Listen to the Surah Al-Ahqaf (الأحقاف) quranic recitation by multiple Qaris. Learn the truth of Tawhid, Quranic revelation, resurrection, patience, and the warning from the people of 'Ad."},"heading":{"title":"","description":""},"lessons":["Believe firmly in Tawhid and worship Allah alone without partners.","The story of the people of 'Ad teaches that pride and rejection of Allah’s message lead to loss.","Surah Al-Ahqaf reminds believers to honor their parents and make sincere dua for them.","The Quran is guidance for both humans and jinn, and sincere hearts accept its truth.","Be patient in calling to the truth, just as the messengers were patient with rejection."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="48" ht="46" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Muhammad [47] - Arabic, Translation &amp; Tafsir | محمد","description":"Read the Surah Muhammad [47] with translation and Tafsir. Listen to the Surah Muhammad (محمد) quranic recitation by multiple Qaris. Learn faith, obedience to Allah, sincerity, and the difference between true believers and hypocrites."},"heading":{"title":"","description":""},"lessons":["True faith must be shown through obedience to Allah and sincere good deeds.","Believers should stay firm during hardship and trust Allah’s help.","Hypocrisy weakens the heart and leads people away from clear guidance.","The Surah teaches respect for the Prophet Muhammad and the message revealed to him.","Worldly life is temporary, so Muslims should seek forgiveness and prepare for the Hereafter."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="49" ht="46" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Fath [48] - Arabic, Translation &amp; Tafsir | الفتح","description":"Read the Surah Al-Fath [48] with translation and Tafsir. Listen to the Surah Al-Fath (الفتح) quranic recitation by multiple Qaris. Learn the divine victory, obedience to Allah, peace, forgiveness, and the qualities of true believers."},"heading":{"title":"","description":""},"lessons":["True victory comes from Allah, even when events first seem difficult or delayed.","Believers should trust Allah’s wisdom and remain patient during trials.","Obedience to Allah and His Messenger brings peace, guidance, and success.","Sincere faith is shown through loyalty, sacrifice, and good character.","Allah praises the believers who are firm against falsehood and merciful among themselves."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="50" ht="46" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Hujurat [49] - Arabic, Translation &amp; Tafsir | الحجرات","description":"Read the Surah Al-Hujurat [49] with translation and Tafsir. Listen to the Surah Al-Hujurat (الحجرات) quranic recitation by multiple Qaris. Learn Islamic manners, brotherhood, social ethics, and true faith."},"heading":{"title":"","description":""},"lessons":["Respect Allah and His Messenger صلى الله عليه وسلم by following divine guidance with humility.","Verify news before sharing it to avoid harm, confusion, and injustice.","Reconcile between believers and protect the unity of the Muslim community.","Avoid mockery, suspicion, spying, and backbiting, as these damage faith and society.","True honor is based on taqwa, not race, tribe, wealth, or social status."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="51" ht="46" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Qaf [50] - Arabic, Translation &amp; Tafsir | ق","description":"Read the Surah Qaf [50] with translation and Tafsir. Listen to the Surah Qaf (ق) quranic recitation by multiple Qaris. Learn about resurrection, accountability, death, and the Day of Judgment."},"heading":{"title":"","description":""},"lessons":["Believe firmly in resurrection and the Day of Judgment, as Allah will bring every soul back to life.","Remember that every word and deed is recorded, so speak and act with care.","Reflect on Allah’s creation as a sign of His power, knowledge, and control.","Prepare for death by living with faith, repentance, and obedience to Allah.","Take warning from past nations who rejected the truth and faced Allah’s judgment."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="52" ht="46" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Adh-Dhariyat [51] - Arabic, Translation &amp; Tafsir | الذاريات","description":"Read the Surah Adh-Dhariyat [51] with translation and Tafsir. Listen to the Surah Adh-Dhariyat (الذاريات) quranic recitation by multiple Qaris. Learn about Allah’s signs, the truth of Resurrection, and the purpose of worship."},"heading":{"title":"","description":""},"lessons":["Believe firmly in the Hereafter, because Resurrection and accountability are true.","Reflect on Allah’s signs in the sky, earth, and within ourselves to strengthen faith.","Remember that the main purpose of human life is to worship Allah alone.","Learn from the stories of earlier nations who rejected the messengers and faced consequences.","Trust Allah as the true Provider and avoid letting worldly worries weaken worship."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="53" ht="46" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah At-Tur [52] - Arabic, Translation &amp; Tafsir | الطور","description":"Read the Surah At-Tur [52] with translation and Tafsir. Listen to the Surah At-Tur (الطور) quranic recitation by multiple Qaris. Learn about the certainty of the Day of Judgment, resurrection, and Allah’s warning to those who reject the truth."},"heading":{"title":"","description":""},"lessons":["The Day of Judgment is certain, and every person will answer for their deeds.","Rejecting Allah’s signs leads to loss, while faith and righteousness bring safety.","The Quran is not poetry or human speech; it is divine guidance from Allah.","Believers should remain patient and trust Allah when facing denial or opposition.","Remembering Allah and glorifying Him strengthens faith in daily life."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="54" ht="46" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah An-Najm [53] - Arabic, Translation &amp; Tafsir | النجم","description":"Read the Surah An-Najm [53] with translation and Tafsir. Listen to the Surah An-Najm (النجم) quranic recitation by multiple Qaris. Learn its main theme: certainty of divine revelation, rejection of false worship, and accountability before Allah."},"heading":{"title":"","description":""},"lessons":["True guidance comes from Allah, and the Quran is revelation, not personal speech or desire.","A believer must reject false worship and turn sincerely to Allah alone.","Every person is responsible for their own deeds and will be judged with perfect justice.","Worldly life should not distract people from the Hereafter and meeting Allah.","Humility before Allah is shown through worship, prayer, and sincere prostration."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="55" ht="46" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Qamar [54] - Arabic, Translation &amp; Tafsir | القمر","description":"Read the Surah Al-Qamar [54] with translation and Tafsir. Listen to the Surah Al-Qamar (القمر) quranic recitation by multiple Qaris. Learn its warning about the Last Hour, Allah’s signs, and the result of rejecting divine guidance."},"heading":{"title":"","description":""},"lessons":["The Day of Judgment is real, and every person should prepare for it with faith and good deeds.","Rejecting Allah’s messengers leads to loss, as shown through the stories of past nations.","The Quran is made easy for remembrance, so believers should recite, understand, and follow it.","Allah’s signs are clear, but pride and denial can stop people from accepting the truth.","True success belongs to the righteous who fear Allah and live with accountability."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="56" ht="46" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Ar-Rahman [55] - Arabic, Translation &amp; Tafsir | الرحمن","description":"Read the Surah Ar-Rahman [55] with translation and Tafsir. Listen to the Surah Ar-Rahman (الرحمن) quranic recitation by multiple Qaris. Learn about Allah’s mercy, blessings, justice, gratitude, and the reality of the Hereafter."},"heading":{"title":"","description":""},"lessons":["Allah’s mercy is seen in creation, guidance, sustenance, and the balance He placed in the universe.","Gratitude is a core lesson, shown through the repeated reminder: which of Allah’s favors will you deny?","Human beings and jinn are both accountable before Allah and will face judgment.","The Surah teaches fairness and balance, especially through the command not to cheat in measure and weight.","Paradise is prepared for those who fear standing before their Lord and live with faith and obedience."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="57" ht="46" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Waqiah [56] - Arabic, Translation &amp; Tafsir | الواقعة","description":"Read the Surah Al-Waqiah [56] with translation and Tafsir. Listen to the Surah Al-Waqiah (الواقعة) quranic recitation by multiple Qaris. Learn about the certainty of the Day of Judgment, resurrection, and human accountability."},"heading":{"title":"","description":""},"lessons":["The Day of Judgment is certain, and every person will stand before Allah for accountability.","True success comes from faith, righteous deeds, and being among those who are close to Allah.","Worldly status will not matter in the Hereafter; only belief and deeds will have value.","Allah’s signs in creation, food, water, fire, and life remind us of His power and mercy.","The Quran is a noble revelation, so it should be recited, respected, understood, and followed."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="58" ht="46" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Hadid [57] - Arabic, Translation &amp; Tafsir | الحديد","description":"Read the Surah Al-Hadid [57] with translation and Tafsir. Listen to the Surah Al-Hadid (الحديد) quranic recitation by multiple Qaris. Learn the power of Allah, faith, charity, justice, and the true value of worldly life."},"heading":{"title":"","description":""},"lessons":["Allah owns the heavens and the earth, so believers should trust Him and live with humility.","True faith is shown through sincere belief, good deeds, and spending in the way of Allah.","Worldly life is temporary, so Muslims should not let wealth, pride, or desires distract them from the Hereafter.","Hearts can become hard when people forget Allah, so regular remembrance and Quran reflection are needed.","Justice, guidance, and strength are blessings from Allah and should be used for truth and righteousness."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="59" ht="46" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Mujadila [58] - Arabic, Translation &amp; Tafsir | المجادلة","description":"Read the Surah Al-Mujadila [58] with translation and Tafsir. Listen to the Surah Al-Mujadila (المجادلة) quranic recitation by multiple Qaris. Learn how Allah hears every complaint, sets family and social laws, and teaches sincere faith and proper conduct."},"heading":{"title":"","description":""},"lessons":["Allah hears every sincere complaint, even when people feel unheard or weak.","Family matters must be handled with justice, mercy, and obedience to Allah’s commands.","Secret talks should never be used for sin, harm, or spreading fear among believers.","True faith requires loyalty to Allah, His Messenger, and the values of Islam.","Good manners, respect, and discipline are part of Islamic guidance in daily life."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="60" ht="46" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Hashr [59] - Arabic, Translation &amp; Tafsir | الحشر","description":"Read the Surah Al-Hashr [59] with translation and Tafsir. Listen to the Surah Al-Hashr (الحشر) quranic recitation by multiple Qaris. Learn faith, trust in Allah, unity, charity, and Allah’s beautiful names."},"heading":{"title":"","description":""},"lessons":["Allah has complete power over all affairs, and believers should place their trust in Him.","Muslims should support one another with sincerity, generosity, and love for the sake of Allah.","Wealth should be used with justice and should not remain only among the rich.","Hypocrisy, false promises, and betrayal lead to loss in this life and the Hereafter.","Reflecting on Allah’s beautiful names strengthens faith, humility, and worship."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="61" ht="46" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Mumtahanah [60] - Arabic, Translation &amp; Tafsir | الممتحنة","description":"Read the Surah Al-Mumtahanah [60] with translation and Tafsir. Listen to the Surah Al-Mumtahanah (الممتحنة) quranic recitation by multiple Qaris. Learn the Surah's guidance on loyalty to Allah, justice, faith, and relations with others."},"heading":{"title":"","description":""},"lessons":["A believer’s loyalty to Allah and His Messenger should come before personal ties or worldly interests.","Islam teaches justice and kindness toward those who do not fight Muslims or oppose their faith.","Faith may be tested, so Muslims should stay firm, sincere, and careful in their choices.","Muslim women have an honored role in faith, pledge, and responsibility before Allah.","The Surah teaches balance: protect faith while dealing with others fairly and wisely."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="62" ht="46" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah As-Saff [61] - Arabic, Translation &amp; Tafsir | الصف","description":"Read the Surah As-Saff [61] with translation and Tafsir. Listen to the Surah As-Saff (الصف) quranic recitation by multiple Qaris. Learn the importance of sincere faith, unity, and striving in Allah’s cause."},"heading":{"title":"","description":""},"lessons":["Faith should be supported by honest actions, not only words.","Muslims should stand together with unity and discipline in serving Allah.","Allah loves those who strive sincerely for truth and righteousness.","The message of Islam confirms the mission of earlier prophets, including Prophet Musa and Prophet Isa.","True success comes through belief in Allah, obedience to His Messenger, and sincere effort in His path."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="63" ht="46" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Jumu'ah [62] - Arabic, Translation &amp; Tafsir | الجمعة","description":"Read the Surah Al-Jumu'ah [62] with translation and Tafsir. Listen to the Surah Al-Jumu'ah (الجمعة) quranic recitation by multiple Qaris. Learn the importance of Friday prayer, sincere obedience, and remembering Allah while seeking His bounty."},"heading":{"title":"","description":""},"lessons":["Allah is perfect, all-powerful, and worthy of constant glorification.","True guidance means learning Allah’s message and acting upon it, not only carrying knowledge.","The Friday prayer is an important public act of worship that should be given priority over trade and daily work.","Muslims should remember Allah often while also seeking lawful provision after worship.","Worldly gain should never distract a believer from obedience, prayer, and the remembrance of Allah."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="64" ht="46" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Munafiqun [63] - Arabic, Translation &amp; Tafsir | المنافقون","description":"Read the Surah Al-Munafiqun [63] with translation and Tafsir. Listen to the Surah Al-Munafiqun (المنافقون) quranic recitation by multiple Qaris. Learn the warning against hypocrisy and the call to sincere faith, remembrance of Allah, and righteous spending."},"heading":{"title":"","description":""},"lessons":["True faith must be sincere in the heart, not only spoken by the tongue.","Lying, pride, and false promises are signs that can lead a person away from Allah.","Wealth and children should never distract believers from the remembrance of Allah.","Spend in the way of Allah before death comes, because regret will not help after life ends.","Believers should stay alert against hypocrisy and ask Allah for a truthful heart."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="65" ht="46" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah At-Taghabun [64] - Arabic, Translation &amp; Tafsir | التغابن","description":"Read the Surah At-Taghabun [64] with translation and Tafsir. Listen to the Surah At-Taghabun (التغابن) quranic recitation by multiple Qaris. Learn about Allah’s power, true faith, the Day of Mutual Loss and Gain, and sincere obedience."},"heading":{"title":"","description":""},"lessons":["Allah knows everything, including what people hide and what they show.","True faith means believing in Allah, obeying His Messenger, and preparing for the Hereafter.","The Day of Taghabun reminds us that real success or loss will be clear on the Day of Judgment.","Wealth, children, and family can be tests, so a believer should stay firm in obedience to Allah.","Giving in the way of Allah with sincerity brings spiritual growth and reward."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="66" ht="46" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah At-Talaq [65] - Arabic, Translation &amp; Tafsir | سورة الطلاق","description":"Read the Surah At-Talaq [65] with translation and Tafsir. Listen to the Surah At-Talaq (سورة الطلاق) quranic recitation by multiple Qaris. Learn Islamic guidance on divorce, waiting periods, family responsibility, taqwa, and trust in Allah."},"heading":{"title":"","description":""},"lessons":["Divorce must be handled with fear of Allah, fairness, and respect for the limits set in the Holy Quran.","Believers should follow the rules of iddah, maintenance, and housing with justice and care.","Taqwa brings ease, provision, and a way out from hardship by Allah’s permission.","Trust in Allah does not mean ignoring duties; it means obeying Him while relying on His help.","Family matters should be settled with kindness, responsibility, and awareness of the Hereafter."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="67" ht="46" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah At-Tahrim [66] - Arabic, Translation &amp; Tafsir | التحريم","description":"Read the Surah At-Tahrim [66] with translation and Tafsir. Listen to the Surah At-Tahrim (التحريم) quranic recitation by multiple Qaris. Learn the importance of sincere repentance, family responsibility, and obedience to Allah."},"heading":{"title":"","description":""},"lessons":["Do not forbid what Allah has made lawful without a valid reason.","Family life should be built on faith, trust, responsibility, and obedience to Allah.","Sincere repentance means leaving sin, feeling regret, and returning to Allah with a clean heart.","A person is judged by their own faith and deeds, even if they are close to righteous people.","The examples of Maryam and the wife of Pharaoh show strength, purity, and firm belief in Allah."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="68" ht="46" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Mulk [67] - Arabic, Translation &amp; Tafsir | الملك","description":"Read the Surah Al-Mulk [67] with translation and Tafsir. Listen to the Surah Al-Mulk (الملك) quranic recitation by multiple Qaris. Learn Allah’s absolute sovereignty, the purpose of life and death, and accountability in the Hereafter."},"heading":{"title":"","description":""},"lessons":["Allah alone owns all power, authority, and control over the heavens and the earth.","Life and death are a test to show who does the best deeds with sincerity and obedience.","The beauty and order of creation remind believers to reflect on Allah’s signs.","Denying the Hereafter leads to loss, while faith brings awareness, humility, and hope.","True security comes from trusting Allah, not from worldly strength or false confidence."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="69" ht="46" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Qalam [68] - Arabic, Translation &amp; Tafsir | القلم","description":"Read the Surah Al-Qalam [68] with translation and Tafsir. Listen to the Surah Al-Qalam (القلم) quranic recitation by multiple Qaris. Learn the truth of revelation, noble character, patience, and warning against arrogance."},"heading":{"title":"","description":""},"lessons":["Good character is a sign of true faith, as Allah praises the Prophet Muhammad صلى الله عليه وسلم for his noble manners.","Muslims should remain patient when facing rejection, insults, or hardship for the sake of truth.","Wealth and success are tests from Allah, and arrogance can lead to loss and regret.","The story of the garden owners teaches us to thank Allah and remember the rights of the poor.","The Day of Judgment is real, and every person will be accountable for their choices."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="70" ht="46" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Haqqah [69] - Arabic, Translation &amp; Tafsir | الحاقة","description":"Read the Surah Al-Haqqah [69] with translation and Tafsir. Listen to the Surah Al-Haqqah (الحاقة) quranic recitation by multiple Qaris. Learn the certainty of the Day of Judgment, accountability, and the truth of the Quran"},"heading":{"title":"","description":""},"lessons":["The Day of Judgment is certain, and every person will face their deeds.","Rejecting Allah’s signs led earlier nations to severe consequences.","The Quran is true revelation from Allah, not poetry or human speech.","Success belongs to those who receive their record in the right hand through faith and righteous deeds.","Worldly power and wealth cannot save anyone from Allah’s judgment."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="71" ht="46" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Ma'arij [70] - Arabic, Translation &amp; Tafsir | المعارج","description":"Read the Surah Al-Ma'arij [70] with translation and Tafsir. Listen to the Surah Al-Ma'arij (المعارج) quranic recitation by multiple Qaris. Learn about the Day of Judgment, human impatience, and the qualities of sincere believers."},"heading":{"title":"","description":""},"lessons":["The Day of Judgment is certain, even if people deny it or think it is far away.","Human beings can be impatient and anxious, but faith and prayer help build patience.","True believers are regular in prayer and mindful of their duties to Allah.","Islam teaches care for the needy by giving them their rightful share.","The Surah reminds us to guard our character, promises, trusts, and moral purity."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="72" ht="46" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Nuh [71] - Arabic, Translation &amp; Tafsir | نوح","description":"Read the Surah Nuh [71] with translation and Tafsir. Listen to the Surah Nuh (نوح) quranic recitation by multiple Qaris. Learn the message of Prophet Nuh, patience in dawah, repentance, and warning against shirk."},"heading":{"title":"","description":""},"lessons":["Call people to Allah with patience, wisdom, and sincerity, even when results are delayed.","Repentance and seeking forgiveness bring Allah’s mercy, blessings, and spiritual growth.","Shirk and arrogance lead people away from truth and divine guidance.","A believer should remain firm in faith when facing rejection or hardship.","True success comes from obeying Allah and following the guidance of His messengers."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="73" ht="46" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Jinn [72] - Arabic, Translation &amp; Tafsir | الجن","description":"Read the Surah Al-Jinn [72] with translation and Tafsir. Listen to the Surah Al-Jinn (الجن) quranic recitation by multiple Qaris. Learn how the Quran guides humans and jinn to Tawhid, faith, and accountability."},"heading":{"title":"","description":""},"lessons":["The Quran is guidance for both humans and jinn, calling all creation to worship Allah alone.","True faith begins with accepting Tawhid and avoiding shirk in every form.","The unseen world belongs to Allah’s knowledge, and no one knows it except what Allah allows.","The Prophet Muhammad صلى الله عليه وسلم was sent to convey Allah’s message, not to control benefit, harm, or guidance by himself.","Every being is accountable to Allah and will face the result of belief, disbelief, and actions."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="74" ht="46" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Muzzammil [73] - Arabic, Translation &amp; Tafsir | المزمل","description":"Read the Surah Al-Muzzammil [73] with translation and Tafsir. Listen to the Surah Al-Muzzammil (المزمل) quranic recitation by multiple Qaris. Learn the importance of night prayer, patient devotion, and steady Quran recitation."},"heading":{"title":"","description":""},"lessons":["Stand in night prayer to build a stronger connection with Allah.","Recite the Quran slowly and clearly with reflection and respect.","Be patient when facing hardship, rejection, or pressure.","Trust Allah while staying firm in worship and good actions.","Give charity, seek forgiveness, and prepare for the Hereafter."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="75" ht="46" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Muddathir [74] - Arabic, Translation &amp; Tafsir | المدثر","description":"Read the Surah Al-Muddathir [74] with translation and Tafsir. Listen to the Surah Al-Muddathir (المدثر) quranic recitation by multiple Qaris. Learn the call to warn people, worship Allah alone, purify the soul, and remember the Day of Judgment."},"heading":{"title":"","description":""},"lessons":["A believer should rise for the sake of Allah and share the truth with wisdom.","True worship begins with glorifying Allah and keeping the heart and actions pure.","Arrogance, denial, and love of worldly status can block a person from guidance.","Every soul is responsible for its choices and will face accountability on the Day of Judgment.","The Quran is a clear reminder, but only those who sincerely seek guidance benefit from it."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="76" ht="46" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Qiyamah [75] - Arabic, Translation &amp; Tafsir | القيامة","description":"Read the Surah Al-Qiyamah [75] with translation and Tafsir. Listen to the Surah Al-Qiyamah (القيامة) quranic recitation by multiple Qaris. Learn about resurrection, accountability, and the certainty of the Last Day."},"heading":{"title":"","description":""},"lessons":["Believe firmly in the Day of Resurrection and prepare for accountability before Allah.","Remember that every action, open or hidden, will be known and judged by Allah.","Do not follow desires blindly, because worldly life is temporary and the Hereafter is lasting.","Trust that Allah has full power to recreate human beings after death.","Listen to the Quran with attention and seek guidance from its message."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="77" ht="46" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Insan [76] - Arabic, Translation &amp; Tafsir | الإنسان","description":"Read the Surah Al-Insan [76] with translation and Tafsir. Listen to the Surah Al-Insan (الإنسان) quranic recitation by multiple Qaris. Learn Allah’s guidance on human creation, gratitude, patience, and the reward of the righteous."},"heading":{"title":"","description":""},"lessons":["Human life begins from a humble origin, so a believer should stay grateful and humble before Allah.","Allah has shown people the path of guidance, and each person is responsible for choosing gratitude over denial.","True righteousness includes feeding the needy, caring for orphans, and helping others sincerely for Allah’s sake.","Patience in worship and obedience brings peace, strength, and hope in Allah’s reward.","The Surah reminds believers that Paradise is a real reward for faith, sincerity, and righteous deeds."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="78" ht="46" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Mursalat [77] - Arabic, Translation &amp; Tafsir | المرسلات","description":"Read the Surah Al-Mursalat [77] with translation and Tafsir. Listen to the Surah Al-Mursalat (المرسلات) quranic recitation by multiple Qaris. Learn about the certainty of the Day of Judgment, resurrection, and Allah’s warning to those who deny the truth."},"heading":{"title":"","description":""},"lessons":["The Day of Judgment is certain, and every person will be held accountable for their deeds.","Allah shows signs of His power in creation, life, death, and the order of the universe.","Denying the truth after clear warnings leads to loss in this life and the Hereafter.","The righteous will be honored by Allah with peace, shade, and blessings in Paradise.","Surah Al-Mursalat teaches believers to take the Quran seriously and prepare for the Hereafter."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="79" ht="46" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah An-Naba [78] - Arabic, Translation &amp; Tafsir | النبأ","description":"Read the Surah An-Naba [78] with translation and Tafsir. Listen to the Surah An-Naba (النبأ) quranic recitation by multiple Qaris. Learn about resurrection, the Day of Judgment, and accountability before Allah."},"heading":{"title":"","description":""},"lessons":["Believe firmly in resurrection and the Day of Judgment, as every person will be brought back for accountability.","Reflect on the signs of Allah in creation, such as the earth, mountains, sleep, night, day, rain, and plants.","Prepare for the Hereafter through faith, obedience, and righteous deeds before the Day of Decision arrives.","Understand that Paradise and Hell are real outcomes based on belief, rejection, and deeds.","Take the Quranic warning seriously and live with awareness of returning to Allah."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="80" ht="46" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah An-Nazi'at [79] - Arabic, Translation &amp; Tafsir | النازعات","description":"Read the Surah An-Nazi'at [79] with translation and Tafsir. Listen to the Surah An-Nazi'at (النازعات) quranic recitation by multiple Qaris. Learn the certainty of resurrection, the Day of Judgment, and accountability before Allah."},"heading":{"title":"","description":""},"lessons":["The resurrection is certain, and every soul will return to Allah for judgment.","Worldly power and pride cannot save anyone from Allah's punishment, as shown in the story of Pharaoh.","The signs in creation remind believers of Allah's power and wisdom.","A believer should prepare for the Hereafter by fearing Allah and controlling sinful desires.","The exact time of the Last Hour is known only to Allah."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="81" ht="46" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Abasa [80] - Arabic, Translation &amp; Tafsir | عبس","description":"Read the Surah Abasa [80] with translation and Tafsir. Listen to the Surah Abasa (عبس) quranic recitation by multiple Qaris. Learn the main theme of sincere guidance, accountability, Resurrection, and preparing for the Hereafter."},"heading":{"title":"","description":""},"lessons":["Guidance is for those who sincerely seek it, no matter their social status.","A believer should treat every seeker of truth with care, respect, and patience.","Worldly rank and influence should never be valued above faith and righteousness.","Allah reminds people to reflect on creation, food, life, death, and the Resurrection.","The Surah teaches accountability and warns that every person will face the Day of Judgment."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="82" ht="46" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah At-Takwir [81] - Arabic, Translation &amp; Tafsir | التكوير","description":"Read the Surah At-Takwir [81] with translation and Tafsir. Listen to the Surah At-Takwir (التكوير) quranic recitation by multiple Qaris. Learn about the Day of Judgment, human accountability, and the truth of Quranic revelation."},"heading":{"title":"","description":""},"lessons":["The Day of Judgment is real, and every person will face the result of their deeds.","The signs of the Last Day remind believers to live with faith, humility, and responsibility.","The Quran is true revelation from Allah, delivered through the trusted angel Jibril.","The Prophet Muhammad صلى الله عليه وسلم is not a poet or madman; he is the honest Messenger of Allah.","Human beings should choose the straight path by following Allah’s guidance."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="83" ht="46" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Infitar [82] - Arabic, Translation &amp; Tafsir | الإنفطار","description":"Read the Surah Al-Infitar [82] with translation and Tafsir. Listen to the Surah Al-Infitar (الإنفطار) quranic recitation by multiple Qaris. Learn about the Day of Judgment, human accountability, and the record of deeds."},"heading":{"title":"","description":""},"lessons":["The Day of Judgment is certain, and every person will see the result of their deeds.","Allah reminds humans not to be deceived by worldly life or become ungrateful to their Creator.","Every action is recorded by noble angels, so Muslims should live with honesty and awareness.","The righteous will receive lasting reward, while the wicked will face the result of their denial.","Surah Al-Infitar teaches accountability, humility, and preparation for the Hereafter."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="84" ht="46" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Mutaffifin [83] - Arabic, Translation &amp; Tafsir | المطففين","description":"Read the Surah Al-Mutaffifin [83] with translation and Tafsir. Listen to the Surah Al-Mutaffifin (المطففين) quranic recitation by multiple Qaris. Learn the warning against dishonesty, denial of the Last Day, and the reward of the righteous."},"heading":{"title":"","description":""},"lessons":["Honesty in trade, business, and daily dealings is a serious part of Islamic faith.","The Day of Judgment is real, and every deed is recorded with complete justice.","Cheating others, even in small matters, is a sign of weak belief and moral failure.","The righteous are honored by Allah, while those who mock believers will face regret.","A Muslim should live with accountability, knowing that Allah sees every action."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="85" ht="46" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Inshiqaq [84] - Arabic, Translation &amp; Tafsir | الانشقاق","description":"Read the Surah Al-Inshiqaq [84] with translation and Tafsir. Listen to the Surah Al-Inshiqaq (الانشقاق) quranic recitation by multiple Qaris. Learn about the certainty of the Day of Judgment, human accountability, and the final return to Allah."},"heading":{"title":"","description":""},"lessons":["The Day of Judgment is certain, and every person will return to Allah for accountability.","Good deeds matter, because each person will receive a record of what they earned in life.","Those who lived with faith and obedience will find ease and joy in the Hereafter.","Ignoring the Quran and refusing to submit to Allah leads to serious loss.","The changing sky, earth, and human life remind us of Allah’s complete power."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="86" ht="46" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Buruj [85] - Arabic, Translation &amp; Tafsir | البروج","description":"Read the Surah Al-Buruj [85] with translation and Tafsir. Listen to the Surah Al-Buruj (البروج) quranic recitation by multiple Qaris. Learn Allah's power, justice, patience during trials, and the truth of the preserved Quran."},"heading":{"title":"","description":""},"lessons":["Allah is fully aware of the oppression faced by believers and will judge every deed with perfect justice.","True faith may be tested, but patience and trust in Allah keep the believer firm.","The story of the People of the Ditch teaches that harming believers for their faith is a grave sin.","Allah's power is complete, and no oppressor can escape His knowledge or punishment.","The Quran is honored and protected, as Allah describes it as a glorious Quran in a preserved tablet."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="87" ht="46" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah At-Tariq [86] - Arabic, Translation &amp; Tafsir | الطارق","description":"Read the Surah At-Tariq [86] with translation and Tafsir. Listen to the Surah At-Tariq (الطارق) quranic recitation by multiple Qaris. Learn about Allah's power over creation, resurrection, and human accountability."},"heading":{"title":"","description":""},"lessons":["Allah watches over every soul, so a believer should live with sincerity and awareness.","Human creation is a clear sign of Allah's power to bring people back to life after death.","Surah At-Tariq teaches that the Day of Judgment is real, and hidden actions will be made known.","The Quran is a decisive and serious message, not something to be taken lightly.","Believers should trust Allah's plan and avoid being misled by those who reject the truth."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="88" ht="46" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-A'la [87] - Arabic, Translation &amp; Tafsir | الأعلى","description":"Read the Surah Al-A'la [87] with translation and Tafsir. Listen to the Surah Al-A'la (الأعلى) quranic recitation by multiple Qaris. Learn Allah's greatness, divine guidance, purification, and the lasting value of the Hereafter."},"heading":{"title":"","description":""},"lessons":["Glorify Allah, the Most High, and remember His perfect power over creation.","True success comes through purification, faith, prayer, and remembering Allah.","The Hereafter is better and longer lasting than the life of this world.","The Quran is a reminder, and those who fear Allah benefit from its guidance.","Allah guides His servants and knows what is hidden and what is open."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="89" ht="46" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Ghashiyah [88] - Arabic, Translation &amp; Tafsir | الغاشية","description":"Read the Surah Al-Ghashiyah [88] with translation and Tafsir. Listen to the Surah Al-Ghashiyah (الغاشية) quranic recitation by multiple Qaris. Learn about the Day of Judgment, Allah's signs in creation, and the Prophet's duty to remind."},"heading":{"title":"","description":""},"lessons":["The Day of Judgment is real, and every person will face the result of their deeds.","True success belongs to those who believe, worship Allah, and prepare for the Hereafter.","Allah invites people to reflect on creation, such as camels, the sky, mountains, and the earth.","The Prophet’s role was to remind people clearly, while guidance and judgment belong to Allah.","Worldly hardship or ease is temporary, but the life of the Hereafter is lasting."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="90" ht="46" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Fajr [89] - Arabic, Translation &amp; Tafsir | الفجر","description":"Read the Surah Al-Fajr [89] with translation and Tafsir. Listen to the Surah Al-Fajr (الفجر) quranic recitation by multiple Qaris. Learn about Allah's justice, the test of wealth and hardship, and the peaceful return of the righteous soul."},"heading":{"title":"","description":""},"lessons":["Worldly power and wealth cannot protect anyone from Allah’s judgment.","Hardship and comfort are both tests from Allah, not signs of honor or disgrace by themselves.","Islam teaches care for orphans, the poor, and those in need.","The Day of Judgment is real, and every person will see the result of their deeds.","A sincere and peaceful soul will return to Allah with honor and mercy."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="91" ht="46" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Balad [90] - Arabic, Translation &amp; Tafsir | البلد","description":"Read the Surah Al-Balad [90] with translation and Tafsir. Listen to the Surah Al-Balad (البلد) quranic recitation by multiple Qaris. Learn moral responsibility, human struggle, charity, faith, patience, and mercy."},"heading":{"title":"","description":""},"lessons":["Life is a test, and every person must struggle to choose the path of truth and goodness.","True success comes through faith, righteous deeds, patience, and mercy toward others.","Helping the weak, feeding the poor, and caring for orphans are signs of sincere belief.","Wealth and strength should not make a person proud, because Allah knows every action.","The Surah teaches accountability and reminds us that every choice leads toward reward or loss."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="92" ht="46" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Ash-Shams [91] - Arabic, Translation &amp; Tafsir | الشمس","description":"Read the Surah Ash-Shams [91] with translation and Tafsir. Listen to the Surah Ash-Shams (الشمس) quranic recitation by multiple Qaris. Learn the importance of purifying the soul, obeying Allah, and avoiding corruption."},"heading":{"title":"","description":""},"lessons":["True success comes from purifying the soul through faith, obedience, and good deeds.","Corrupting the soul with sin, arrogance, and denial leads to loss.","Allah’s signs in the sun, moon, day, night, earth, and sky remind us of His power.","The story of Thamud teaches us to respect Allah’s commands and His messengers.","Every person is responsible for choosing the path of righteousness or wrongdoing."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="93" ht="46" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Layl [92] - Arabic, Translation &amp; Tafsir | الليل","description":"Read the Surah Al-Layl [92] with translation and Tafsir. Listen to the Surah Al-Layl (الليل) quranic recitation by multiple Qaris. Learn how faith, charity, and taqwa lead to ease, while denial and greed lead to hardship."},"heading":{"title":"","description":""},"lessons":["Allah shows that human efforts are different, and every person is responsible for the path they choose.","Giving for the sake of Allah, having taqwa, and believing in truth lead to ease and success.","Stinginess, pride, and denial of guidance lead a person toward hardship and loss.","Wealth cannot save anyone from accountability when a person turns away from Allah.","True charity is done sincerely for Allah, not for praise, status, or worldly reward."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="94" ht="46" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Ad-Duha [93] - Arabic, Translation &amp; Tafsir | الضحى","description":"Read the Surah Ad-Duha [93] with translation and Tafsir. Listen to the Surah Ad-Duha (الضحى) quranic recitation by multiple Qaris. Learn Allah’s mercy, hope after hardship, gratitude, and care for the orphan and needy."},"heading":{"title":"","description":""},"lessons":["Allah never abandons His servants, even when life feels silent or difficult.","Hardship is not permanent; Allah promises ease, hope, and a better future.","A believer should remember Allah’s past blessings and stay grateful.","Islam teaches kindness to orphans, the needy, and vulnerable people.","Allah’s blessings should be acknowledged with humility and used in good ways."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="95" ht="46" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Ash-Sharh [94] - Arabic, Translation &amp; Tafsir | الشرح","description":"Read the Surah Ash-Sharh [94] with translation and Tafsir. Listen to the Surah Ash-Sharh (الشرح) quranic recitation by multiple Qaris. Learn Allah's comfort to the Prophet, ease after hardship, and devotion to worship"},"heading":{"title":"","description":""},"lessons":["Allah can open the heart and make difficult duties easier for His servants.","Hardship is not permanent, and Allah promises ease along with difficulty.","The Prophet Muhammad's rank and mention were raised by Allah as a special honor.","A believer should stay hopeful, patient, and active during tests.","After finishing important work, a Muslim should turn to Allah in worship and prayer."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="96" ht="46" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah At-Tin [95] - Arabic, Translation &amp; Tafsir | التين","description":"Read the Surah At-Tin [95] with translation and Tafsir. Listen to the Surah At-Tin (التين) quranic recitation by multiple Qaris. Learn how Surah At-Tin teaches human dignity, faith, righteous deeds, accountability, and Allah’s perfect judgment."},"heading":{"title":"","description":""},"lessons":["Allah created the human being in the best form, so life should be lived with gratitude and purpose.","True honor comes through faith and righteous deeds, not only through outward appearance or status.","Those who reject guidance after clear signs will be held accountable before Allah.","Allah is the best and most just Judge, and His judgment is perfect."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="97" ht="46" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Alaq [96] - Arabic, Translation &amp; Tafsir | العلق","description":"Read the Surah Al-Alaq [96] with translation and Tafsir. Listen to the Surah Al-Alaq (العلق) quranic recitation by multiple Qaris. Learn how revelation, knowledge, humility, and prostration guide a believer."},"heading":{"title":"","description":""},"lessons":["Allah honored humanity with knowledge and taught by the pen.","A believer should seek knowledge in the name of Allah, not for pride.","Human beings must remember their humble origin and avoid arrogance.","No one can stop sincere worship, prayer, and obedience to Allah.","True closeness to Allah comes through submission and prostration."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="98" ht="46" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Qadr [97] - Arabic, Translation &amp; Tafsir | سورة القدر","description":"Read the Surah Al-Qadr [97] with translation and Tafsir. Listen to the Surah Al-Qadr (سورة القدر) quranic recitation by multiple Qaris. Learn the greatness of Laylat al-Qadr, the revelation of the Quran, and the peace sent by Allah until dawn."},"heading":{"title":"","description":""},"lessons":["The Quran is a blessed revelation sent by Allah as guidance for all people.","Laylat al-Qadr is a night of great honor, better than a thousand months.","Angels descend by Allah’s command, showing the mercy and greatness of this night.","Believers should seek Allah’s mercy, worship sincerely, and value the last nights of Ramadan.","True peace comes from obeying Allah and staying connected to the Quran."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="99" ht="46" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Bayyinah [98] - Arabic, Translation &amp; Tafsir | البينة","description":"Read the Surah Al-Bayyinah [98] with translation and Tafsir. Listen to the Surah Al-Bayyinah (البينة) quranic recitation by multiple Qaris. Learn the clear evidence of prophethood, sincere worship, and the final outcome of believers and rejecters."},"heading":{"title":"","description":""},"lessons":["Clear guidance from Allah came through the Prophet Muhammad صلى الله عليه وسلم and the Quran, so truth should be accepted with humility.","True religion is based on sincere worship of Allah alone, regular prayer, and giving zakah.","Knowledge alone is not enough; people must act upon clear evidence when it reaches them.","Those who believe and do righteous deeds are honored by Allah and promised lasting reward.","Rejecting clear truth after it becomes known is a serious matter with severe consequences."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="100" ht="46" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Az Zalzalah [99] - Arabic, Translation &amp; Tafsir | الزلزلة","description":"Read the Surah Az Zalzalah [99] with translation and Tafsir. Listen to the Surah Az Zalzalah (الزلزلة) quranic recitation by multiple Qaris. Learn about the Day of Judgment, accountability, and how every deed will be shown."},"heading":{"title":"","description":""},"lessons":["Every person will be held accountable before Allah for their actions.","No good deed is too small to be rewarded by Allah.","No evil deed is too small to be ignored without Allah’s knowledge.","The Day of Judgment is real, and the earth itself will bear witness.","A believer should live carefully, doing good and avoiding sin in daily life."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="101" ht="46" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Adiyat [100] - Arabic, Translation &amp; Tafsir | العاديات","description":"Read the Surah Al-Adiyat [100] with translation and Tafsir. Listen to the Surah Al-Adiyat (العاديات) quranic recitation by multiple Qaris. Learn about human ingratitude, love of wealth, and accountability before Allah."},"heading":{"title":"","description":""},"lessons":["Surah Al-Adiyat teaches that people should not be ungrateful to Allah for His blessings.","The Surah warns against becoming too attached to wealth and worldly gain.","It reminds believers that hidden thoughts, actions, and intentions will be brought out on the Day of Judgment.","The Surah encourages self-checking, sincere faith, and preparing for the meeting with Allah."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="102" ht="46" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Qari'ah [101] - Arabic, Translation &amp; Tafsir | القارعة","description":"Read the Surah Al-Qari'ah [101] with translation and Tafsir. Listen to the Surah Al-Qari'ah (القارعة) quranic recitation by multiple Qaris. Learn about the Day of Judgment, the weighing of deeds, and the final outcome of human actions."},"heading":{"title":"","description":""},"lessons":["The Day of Judgment is real, and every person will face the result of their deeds.","Good deeds done with sincere faith will be weighed and rewarded by Allah.","A light scale of deeds warns us to avoid careless living and disobedience.","This Surah reminds believers to prepare for the Hereafter through faith, prayer, and righteous actions.","Worldly strength and pride will not help anyone when Allah brings the final judgment."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="103" ht="46" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah At-Takathur [102] - Arabic, Translation &amp; Tafsir | التكاثر","description":"Read the Surah At-Takathur [102] with translation and Tafsir. Listen to the Surah At-Takathur (التكاثر) quranic recitation by multiple Qaris. Learn the warning against worldly rivalry, heedlessness, and accountability in the Hereafter."},"heading":{"title":"","description":""},"lessons":["Worldly competition in wealth, status, and numbers can distract the heart from Allah and the Hereafter.","A believer should remember death often, because every person will return to the grave and face accountability.","True certainty about the Hereafter helps a Muslim avoid heedlessness and live with purpose.","Allah will question people about the blessings they enjoyed, so gratitude and responsible use of blessings are required.","Success is not measured by worldly increase, but by faith, obedience, and preparation for the Day of Judgment."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="104" ht="46" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Asr [103] - Arabic, Translation &amp; Tafsir | العصر","description":"Read the Surah Al-Asr [103] with translation and Tafsir. Listen to the Surah Al-Asr (العصر) quranic recitation by multiple Qaris. Learn the value of time, faith, righteous deeds, truth, and patience."},"heading":{"title":"","description":""},"lessons":["Time is a trust from Allah, and every person will be accountable for how they use it.","True success comes through faith in Allah and righteous deeds.","Muslims should advise one another to follow the truth with sincerity and wisdom.","Patience is needed to stay firm on faith, good actions, and truth during tests."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="105" ht="46" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Humazah [104] - Arabic, Translation &amp; Tafsir | الهمزة","description":"Read the Surah Al-Humazah [104] with translation and Tafsir. Listen to the Surah Al-Humazah (الهمزة) quranic recitation by multiple Qaris. Learn the warning against slander, mockery, greed, arrogance, and heedlessness of the Hereafter."},"heading":{"title":"","description":""},"lessons":["Avoid slander, backbiting, and mocking others, as these actions harm both people and faith.","Wealth should not make a person proud or careless about the Hereafter.","A believer must remember that worldly status cannot protect anyone from Allah's judgment.","Surah Al-Humazah teaches accountability for hidden and open sins.","Good character, humility, and respect for others are key parts of Islamic guidance."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="106" ht="46" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Fil [105] - Arabic, Translation &amp; Tafsir | الفيل","description":"Read the Surah Al-Fil [105] with translation and Tafsir. Listen to the Surah Al-Fil (الفيل) quranic recitation by multiple Qaris. Learn Allah’s protection of the Ka'bah and His power over arrogant enemies."},"heading":{"title":"","description":""},"lessons":["Allah protects what He wills, even against powerful armies and rulers.","Pride, arrogance, and oppression can lead to sudden downfall.","True power belongs to Allah, not to wealth, numbers, or military strength.","Believers should trust Allah’s plan, especially during fear and hardship.","Sacred places and acts of worship deserve respect and protection."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="107" ht="46" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Quraysh [106] - Arabic, Translation &amp; Tafsir | قريش","description":"Read the Surah Quraysh [106] with translation and Tafsir. Listen to the Surah Quraysh (قريش) quranic recitation by multiple Qaris. Learn Allah’s blessings of security and provision and the call to worship the Lord of the Ka'bah."},"heading":{"title":"","description":""},"lessons":["Allah’s blessings of food, safety, and ease should lead people to gratitude and worship.","True security and provision come from Allah alone, not from wealth, status, or tribe.","The Lord of the Ka'bah deserves sincere worship because He protects and provides.","Remembering Allah’s favors helps a believer live with humility and thankfulness.","Worldly comfort should not make people forget their duty to obey Allah."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="108" ht="46" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Ma'un [107] - Arabic, Translation &amp; Tafsir | الماعون","description":"Read the Surah Al-Ma'un [107] with translation and Tafsir. Listen to the Surah Al-Ma'un (الماعون) quranic recitation by multiple Qaris. Learn how true faith is shown through sincere prayer, care for the needy, and everyday kindness."},"heading":{"title":"","description":""},"lessons":["True belief in the Hereafter should make a person kind, honest, and responsible.","Caring for orphans and feeding the needy are signs of sincere faith.","Prayer must be performed with attention, humility, and sincerity.","Showing off in worship harms the heart and weakens the value of good deeds.","Even small acts of help and kindness should not be withheld from others."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="109" ht="46" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al Kawthar [108] - Arabic, Translation &amp; Tafsir | الكوثر","description":"Read the Surah Al Kawthar [108] with translation and Tafsir. Listen to the Surah Al Kawthar (الكوثر) quranic recitation by multiple Qaris. Learn how Allah granted abundant good to the Prophet Muhammad صلى الله عليه وسلم and commanded prayer, sacrifice, and trust in Him."},"heading":{"title":"","description":""},"lessons":["Allah’s blessings are vast, and believers should respond with gratitude and worship.","Prayer and sacrifice should be done sincerely for Allah alone.","Worldly insults and opposition cannot harm the honor Allah gives to His Messenger صلى الله عليه وسلم.","True success comes from being connected to Allah, not from wealth, power, or status.","Surah Al Kawthar teaches Muslims to stay patient and trust Allah during hardship."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+    <row r="110" ht="46" customHeight="1">
+      <c r="A110" s="4" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Kafirun [109] - Arabic, Translation &amp; Tafsir | الكافرون","description":"Read the Surah Al-Kafirun [109] with translation and Tafsir. Listen to the Surah Al-Kafirun (الكافرون) quranic recitation by multiple Qaris. Learn the firm message of Tawhid, rejection of shirk, and sincere worship of Allah."},"heading":{"title":"","description":""},"lessons":["Worship must be sincerely for Allah alone, without mixing it with shirk.","A Muslim should stay firm in Tawhid even when facing pressure or compromise.","Islam teaches clear boundaries in belief while maintaining dignity and calm speech.","True faith is not based on pleasing people, but on obeying Allah.","Respectful disagreement does not mean accepting false beliefs as truth."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+    <row r="111" ht="46" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah An-Nasr [110] - Arabic, Translation &amp; Tafsir | النصر","description":"Read the Surah An-Nasr [110] with translation and Tafsir. Listen to the Surah An-Nasr (النصر) quranic recitation by multiple Qaris. Learn Allah’s help, victory, gratitude, and seeking forgiveness."},"heading":{"title":"","description":""},"lessons":["True victory comes only from Allah, so Muslims should stay humble and grateful.","Success should lead a believer to praise Allah, not to pride or arrogance.","Seeking forgiveness is needed even after good deeds and great achievements.","Surah An-Nasr reminds Muslims that Islam is a complete guidance for individuals and communities.","The Surah teaches that worship, gratitude, and repentance should be part of daily life."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+    <row r="112" ht="46" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Lahab [111] - Arabic, Translation &amp; Tafsir | اللهب","description":"Read the Surah Al-Lahab [111] with translation and Tafsir. Listen to the Surah Al-Lahab (اللهب) quranic recitation by multiple Qaris. Learn how arrogance, wealth, and opposition to divine guidance cannot save anyone from Allah’s judgment."},"heading":{"title":"","description":""},"lessons":["Wealth, family status, and power cannot protect anyone from Allah’s judgment.","Open hatred toward truth and guidance leads to loss in this life and the Hereafter.","Islam teaches that honor comes through faith and obedience, not pride or lineage.","Every person is responsible for their own choices, words, and actions.","The Surah reminds believers to stay firm when facing mockery or opposition."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="113" ht="46" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Ikhlas [112] - Arabic, Translation &amp; Tafsir | الإخلاص","description":"Read the Surah Al-Ikhlas [112] with translation and Tafsir. Listen to the Surah Al-Ikhlas (الإخلاص) quranic recitation by multiple Qaris. Learn pure Tawhid, the oneness of Allah, and the foundation of Islamic belief."},"heading":{"title":"","description":""},"lessons":["Allah is One, unique, and unlike anything in creation.","True faith begins with pure Tawhid and worshiping Allah alone.","Allah is eternal, self-sufficient, and free from all needs.","Islam rejects the idea that Allah has parents, children, or equals.","A believer should keep faith sincere and avoid all forms of shirk."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+    <row r="114" ht="46" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah Al-Falaq [113] - Arabic, Translation &amp; Tafsir | الفلق","description":"Read the Surah Al-Falaq [113] with translation and Tafsir. Listen to the Surah Al-Falaq (الفلق) quranic recitation by multiple Qaris. Learn seeking Allah’s protection from the evil of creation, darkness, magic, and envy."},"heading":{"title":"","description":""},"lessons":["Seek refuge in Allah alone, because true protection comes only from Him.","Evil can come from many sources, so a believer should stay spiritually aware.","The Surah teaches protection from harm linked to darkness, envy, and hidden evil.","Envy is dangerous, and Muslims should guard their hearts from jealousy.","Daily remembrance of Allah brings comfort, trust, and spiritual safety."],"faqs":[]}</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+    <row r="115" ht="46" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Surah An-Nas [114] - Arabic, Translation &amp; Tafsir | الناس","description":"Read the Surah An-Nas [114] with translation and Tafsir. Listen to the Surah An-Nas (الناس) quranic recitation by multiple Qaris. Learn how this Surah teaches protection by seeking refuge in Allah from evil whispers and harmful influences."},"heading":{"title":"","description":""},"lessons":["Seek refuge only in Allah, the Lord, King, and God of all mankind.","Recognize that evil whispers can come quietly and must be resisted with faith.","Remember that Shaytan’s influence becomes weak when a believer turns to Allah.","Protect the heart through dhikr, Quran recitation, prayer, and trust in Allah.","Understand that harmful whispers may come from both jinn and people."],"faqs":[]}</t>
         </is>
